--- a/sample_data/output/excel/01_유형별_집계.xlsx
+++ b/sample_data/output/excel/01_유형별_집계.xlsx
@@ -493,31 +493,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>602</v>
       </c>
       <c r="E2" t="n">
-        <v>5832.3199</v>
+        <v>494171.554298761</v>
       </c>
       <c r="F2" t="n">
-        <v>1140.285714285714</v>
+        <v>1266.470099667774</v>
       </c>
       <c r="G2" t="n">
-        <v>22434.11428571428</v>
+        <v>507.0265780730897</v>
       </c>
       <c r="H2" t="n">
-        <v>23806.2</v>
+        <v>6220.230897009967</v>
       </c>
       <c r="I2" t="n">
-        <v>19686.11428571428</v>
+        <v>1015.724252491694</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4958614554171417</v>
+        <v>0.09055388644168433</v>
       </c>
       <c r="K2" t="n">
-        <v>273.5714285714286</v>
+        <v>122.9186046511628</v>
       </c>
       <c r="L2" t="n">
-        <v>609.2</v>
+        <v>362.9136212624585</v>
       </c>
     </row>
     <row r="3">
@@ -535,31 +535,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="E3" t="n">
-        <v>3524.3315</v>
+        <v>182095.950513618</v>
       </c>
       <c r="F3" t="n">
-        <v>763.1304347826087</v>
+        <v>992.1758793969849</v>
       </c>
       <c r="G3" t="n">
-        <v>119724.347826087</v>
+        <v>39229.64824120603</v>
       </c>
       <c r="H3" t="n">
-        <v>112094.6086956522</v>
+        <v>58314.05025125628</v>
       </c>
       <c r="I3" t="n">
-        <v>23739.13043478261</v>
+        <v>9004.025125628141</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8828973733514773</v>
+        <v>0.7691763066041959</v>
       </c>
       <c r="K3" t="n">
-        <v>264.6521739130435</v>
+        <v>177.9095477386935</v>
       </c>
       <c r="L3" t="n">
-        <v>644.1304347826087</v>
+        <v>561.3869346733668</v>
       </c>
     </row>
     <row r="4">
@@ -577,31 +577,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>1467</v>
       </c>
       <c r="E4" t="n">
-        <v>9139.767599999999</v>
+        <v>1275064.45041441</v>
       </c>
       <c r="F4" t="n">
-        <v>3576.04</v>
+        <v>3858.568507157464</v>
       </c>
       <c r="G4" t="n">
-        <v>49014.94</v>
+        <v>4976.468984321745</v>
       </c>
       <c r="H4" t="n">
-        <v>45957.18</v>
+        <v>28623.5269256987</v>
       </c>
       <c r="I4" t="n">
-        <v>23713.14</v>
+        <v>3972.183367416496</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6412462942520222</v>
+        <v>0.2991492254986043</v>
       </c>
       <c r="K4" t="n">
-        <v>268.14</v>
+        <v>233.5446489434219</v>
       </c>
       <c r="L4" t="n">
-        <v>612.3</v>
+        <v>617.8977505112474</v>
       </c>
     </row>
     <row r="5">
@@ -619,31 +619,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>1377</v>
       </c>
       <c r="E5" t="n">
-        <v>4781.0246</v>
+        <v>1387582.712597516</v>
       </c>
       <c r="F5" t="n">
-        <v>4639</v>
+        <v>5991.415395787944</v>
       </c>
       <c r="G5" t="n">
-        <v>120027.0833333333</v>
+        <v>46866.91358024691</v>
       </c>
       <c r="H5" t="n">
-        <v>121087.25</v>
+        <v>86301.70878721859</v>
       </c>
       <c r="I5" t="n">
-        <v>18535.5</v>
+        <v>9188.594045025418</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8630592805933595</v>
+        <v>0.6308618290228362</v>
       </c>
       <c r="K5" t="n">
-        <v>193.4166666666667</v>
+        <v>285.8518518518518</v>
       </c>
       <c r="L5" t="n">
-        <v>591.1666666666666</v>
+        <v>953.1946259985476</v>
       </c>
     </row>
     <row r="6">
@@ -661,31 +661,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>1117</v>
       </c>
       <c r="E6" t="n">
-        <v>7351.0923</v>
+        <v>852059.374444106</v>
       </c>
       <c r="F6" t="n">
-        <v>1369.682926829268</v>
+        <v>1136.401969561325</v>
       </c>
       <c r="G6" t="n">
-        <v>24158.26829268293</v>
+        <v>685.9749328558639</v>
       </c>
       <c r="H6" t="n">
-        <v>26992.75609756097</v>
+        <v>6564.294538943599</v>
       </c>
       <c r="I6" t="n">
-        <v>19714.14634146342</v>
+        <v>767.0519247985676</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4914382634096761</v>
+        <v>0.1378374385640029</v>
       </c>
       <c r="K6" t="n">
-        <v>263.7317073170732</v>
+        <v>138.4341987466428</v>
       </c>
       <c r="L6" t="n">
-        <v>635.609756097561</v>
+        <v>327.7108325872874</v>
       </c>
     </row>
     <row r="7">
@@ -703,31 +703,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>384</v>
       </c>
       <c r="E7" t="n">
-        <v>6216.7917</v>
+        <v>321596.603558138</v>
       </c>
       <c r="F7" t="n">
-        <v>803.375</v>
+        <v>979.3385416666666</v>
       </c>
       <c r="G7" t="n">
-        <v>115049.625</v>
+        <v>35710.76302083334</v>
       </c>
       <c r="H7" t="n">
-        <v>110076.96875</v>
+        <v>43334.515625</v>
       </c>
       <c r="I7" t="n">
-        <v>20831.5625</v>
+        <v>2175.989583333333</v>
       </c>
       <c r="J7" t="n">
-        <v>0.880490579937828</v>
+        <v>0.8479764098262436</v>
       </c>
       <c r="K7" t="n">
-        <v>226.53125</v>
+        <v>218.4427083333333</v>
       </c>
       <c r="L7" t="n">
-        <v>499.4375</v>
+        <v>482.4375</v>
       </c>
     </row>
     <row r="8">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>953</v>
       </c>
       <c r="E8" t="n">
-        <v>13624.4779</v>
+        <v>718031.96706191</v>
       </c>
       <c r="F8" t="n">
-        <v>4042.658536585366</v>
+        <v>2377.614900314795</v>
       </c>
       <c r="G8" t="n">
-        <v>51559.01219512195</v>
+        <v>6541.252885624344</v>
       </c>
       <c r="H8" t="n">
-        <v>49776.10975609756</v>
+        <v>22063.82896117524</v>
       </c>
       <c r="I8" t="n">
-        <v>20200.60975609756</v>
+        <v>1203.211962224554</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6897036720672109</v>
+        <v>0.4593344298822832</v>
       </c>
       <c r="K8" t="n">
-        <v>247.1829268292683</v>
+        <v>248.7985309548793</v>
       </c>
       <c r="L8" t="n">
-        <v>618.6829268292682</v>
+        <v>450.3389296956978</v>
       </c>
     </row>
     <row r="9">
@@ -787,31 +787,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>615</v>
       </c>
       <c r="E9" t="n">
-        <v>8336.438400000001</v>
+        <v>589828.096522618</v>
       </c>
       <c r="F9" t="n">
-        <v>5155.942307692308</v>
+        <v>4165.778861788618</v>
       </c>
       <c r="G9" t="n">
-        <v>118422.3076923077</v>
+        <v>51935.77235772357</v>
       </c>
       <c r="H9" t="n">
-        <v>117149.3846153846</v>
+        <v>86676.2</v>
       </c>
       <c r="I9" t="n">
-        <v>19524.42307692308</v>
+        <v>6490.531707317074</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8687103389501263</v>
+        <v>0.7096442767182232</v>
       </c>
       <c r="K9" t="n">
-        <v>252.7692307692308</v>
+        <v>390.4260162601626</v>
       </c>
       <c r="L9" t="n">
-        <v>602.7307692307693</v>
+        <v>827.0422764227642</v>
       </c>
     </row>
     <row r="10">
@@ -829,31 +829,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>557</v>
       </c>
       <c r="E10" t="n">
-        <v>3985.895</v>
+        <v>458879.1912557</v>
       </c>
       <c r="F10" t="n">
-        <v>1892.227272727273</v>
+        <v>1221.912028725314</v>
       </c>
       <c r="G10" t="n">
-        <v>27813.22727272727</v>
+        <v>446.6068222621185</v>
       </c>
       <c r="H10" t="n">
-        <v>26634.86363636364</v>
+        <v>5614.662477558349</v>
       </c>
       <c r="I10" t="n">
-        <v>18727.04545454546</v>
+        <v>1446.222621184919</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5996873806529807</v>
+        <v>0.06684200853407909</v>
       </c>
       <c r="K10" t="n">
-        <v>259.5454545454546</v>
+        <v>118.3303411131059</v>
       </c>
       <c r="L10" t="n">
-        <v>694.9090909090909</v>
+        <v>375.8438061041293</v>
       </c>
     </row>
     <row r="11">
@@ -871,31 +871,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="E11" t="n">
-        <v>3923.6277</v>
+        <v>159157.573467</v>
       </c>
       <c r="F11" t="n">
-        <v>705.695652173913</v>
+        <v>1002.810344827586</v>
       </c>
       <c r="G11" t="n">
-        <v>121359.1739130435</v>
+        <v>37521.83908045977</v>
       </c>
       <c r="H11" t="n">
-        <v>118624.3043478261</v>
+        <v>47659.97126436781</v>
       </c>
       <c r="I11" t="n">
-        <v>20359.08695652174</v>
+        <v>8577.764367816091</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8751755198625384</v>
+        <v>0.791309664579941</v>
       </c>
       <c r="K11" t="n">
-        <v>213.3478260869565</v>
+        <v>206.8275862068965</v>
       </c>
       <c r="L11" t="n">
-        <v>538.695652173913</v>
+        <v>573.3793103448276</v>
       </c>
     </row>
     <row r="12">
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>1493</v>
       </c>
       <c r="E12" t="n">
-        <v>10056.9974</v>
+        <v>1296835.57385664</v>
       </c>
       <c r="F12" t="n">
-        <v>3825.035714285714</v>
+        <v>4054.607501674481</v>
       </c>
       <c r="G12" t="n">
-        <v>50194.30357142857</v>
+        <v>5029.320830542531</v>
       </c>
       <c r="H12" t="n">
-        <v>53020.44642857143</v>
+        <v>30362.86537173476</v>
       </c>
       <c r="I12" t="n">
-        <v>19634.08928571429</v>
+        <v>4385.841259209645</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6557066716892336</v>
+        <v>0.2812671762841372</v>
       </c>
       <c r="K12" t="n">
-        <v>292.375</v>
+        <v>242.3436034829203</v>
       </c>
       <c r="L12" t="n">
-        <v>669.9285714285714</v>
+        <v>688.8774279973209</v>
       </c>
     </row>
     <row r="13">
@@ -955,31 +955,31 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>1518</v>
       </c>
       <c r="E13" t="n">
-        <v>7432.9913</v>
+        <v>1495920.85426047</v>
       </c>
       <c r="F13" t="n">
-        <v>4974.372093023256</v>
+        <v>6375.630434782609</v>
       </c>
       <c r="G13" t="n">
-        <v>120127.3953488372</v>
+        <v>46073.92028985507</v>
       </c>
       <c r="H13" t="n">
-        <v>118146.2093023256</v>
+        <v>88340.54150197629</v>
       </c>
       <c r="I13" t="n">
-        <v>19511.44186046511</v>
+        <v>8519.414361001318</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8703729254604777</v>
+        <v>0.6125604636149451</v>
       </c>
       <c r="K13" t="n">
-        <v>240.4418604651163</v>
+        <v>282.0046113306983</v>
       </c>
       <c r="L13" t="n">
-        <v>554.0697674418604</v>
+        <v>1018.21277997365</v>
       </c>
     </row>
     <row r="14">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>1078</v>
       </c>
       <c r="E14" t="n">
-        <v>7481.6373</v>
+        <v>800322.4850499</v>
       </c>
       <c r="F14" t="n">
-        <v>1178.217391304348</v>
+        <v>1150.917439703154</v>
       </c>
       <c r="G14" t="n">
-        <v>23699.4347826087</v>
+        <v>628.8200371057513</v>
       </c>
       <c r="H14" t="n">
-        <v>27980</v>
+        <v>6185.497217068646</v>
       </c>
       <c r="I14" t="n">
-        <v>18802.5</v>
+        <v>513.252319109462</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5014145345686554</v>
+        <v>0.1355212161204174</v>
       </c>
       <c r="K14" t="n">
-        <v>267.9130434782609</v>
+        <v>150.7031539888683</v>
       </c>
       <c r="L14" t="n">
-        <v>600.3478260869565</v>
+        <v>344.9378478664193</v>
       </c>
     </row>
     <row r="15">
@@ -1039,31 +1039,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>360</v>
       </c>
       <c r="E15" t="n">
-        <v>3407.2424</v>
+        <v>291541.2845907</v>
       </c>
       <c r="F15" t="n">
-        <v>867.9411764705883</v>
+        <v>1062.508333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>117295.7058823529</v>
+        <v>33917.08333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>113324.0588235294</v>
+        <v>40202.07777777778</v>
       </c>
       <c r="I15" t="n">
-        <v>18566.82352941177</v>
+        <v>2871.472222222222</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8925582663330879</v>
+        <v>0.8649897332519619</v>
       </c>
       <c r="K15" t="n">
-        <v>263.2352941176471</v>
+        <v>256.6166666666667</v>
       </c>
       <c r="L15" t="n">
-        <v>680.0588235294117</v>
+        <v>480.8694444444445</v>
       </c>
     </row>
     <row r="16">
@@ -1081,31 +1081,31 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>1076</v>
       </c>
       <c r="E16" t="n">
-        <v>16373.7455</v>
+        <v>802752.99118207</v>
       </c>
       <c r="F16" t="n">
-        <v>4304.739130434783</v>
+        <v>2492.848513011153</v>
       </c>
       <c r="G16" t="n">
-        <v>48956.6847826087</v>
+        <v>6642.842007434944</v>
       </c>
       <c r="H16" t="n">
-        <v>46748.90217391304</v>
+        <v>20573.34107806691</v>
       </c>
       <c r="I16" t="n">
-        <v>21376.72826086956</v>
+        <v>1341.520446096654</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6515345898095246</v>
+        <v>0.4432555214267294</v>
       </c>
       <c r="K16" t="n">
-        <v>270.9565217391304</v>
+        <v>282.1291821561338</v>
       </c>
       <c r="L16" t="n">
-        <v>616.9130434782609</v>
+        <v>491.2946096654275</v>
       </c>
     </row>
     <row r="17">
@@ -1123,31 +1123,31 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>755</v>
       </c>
       <c r="E17" t="n">
-        <v>8950.8475</v>
+        <v>708565.6657070999</v>
       </c>
       <c r="F17" t="n">
-        <v>4862.2</v>
+        <v>4518.879470198675</v>
       </c>
       <c r="G17" t="n">
-        <v>115457.0545454545</v>
+        <v>51255.03311258278</v>
       </c>
       <c r="H17" t="n">
-        <v>114755.8545454545</v>
+        <v>90599.09801324503</v>
       </c>
       <c r="I17" t="n">
-        <v>21049.65454545454</v>
+        <v>6578.625165562914</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8516646208553517</v>
+        <v>0.6782858011379456</v>
       </c>
       <c r="K17" t="n">
-        <v>238.9090909090909</v>
+        <v>440.0092715231788</v>
       </c>
       <c r="L17" t="n">
-        <v>518.6545454545454</v>
+        <v>891.7615894039735</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/output/excel/01_유형별_집계.xlsx
+++ b/sample_data/output/excel/01_유형별_집계.xlsx
@@ -493,31 +493,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>602</v>
+        <v>446</v>
       </c>
       <c r="E2" t="n">
-        <v>494171.554298761</v>
+        <v>363491.079726615</v>
       </c>
       <c r="F2" t="n">
-        <v>1266.470099667774</v>
+        <v>1089.730941704036</v>
       </c>
       <c r="G2" t="n">
-        <v>507.0265780730897</v>
+        <v>499.9327354260089</v>
       </c>
       <c r="H2" t="n">
-        <v>6220.230897009967</v>
+        <v>5157.706278026906</v>
       </c>
       <c r="I2" t="n">
-        <v>1015.724252491694</v>
+        <v>979.4730941704036</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09055388644168433</v>
+        <v>0.1009874074271771</v>
       </c>
       <c r="K2" t="n">
-        <v>122.9186046511628</v>
+        <v>115.4192825112108</v>
       </c>
       <c r="L2" t="n">
-        <v>362.9136212624585</v>
+        <v>338.4237668161435</v>
       </c>
     </row>
     <row r="3">
@@ -535,31 +535,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="E3" t="n">
-        <v>182095.950513618</v>
+        <v>155916.975711518</v>
       </c>
       <c r="F3" t="n">
-        <v>992.1758793969849</v>
+        <v>904.0670731707318</v>
       </c>
       <c r="G3" t="n">
-        <v>39229.64824120603</v>
+        <v>38760.36585365854</v>
       </c>
       <c r="H3" t="n">
-        <v>58314.05025125628</v>
+        <v>61248.89024390244</v>
       </c>
       <c r="I3" t="n">
-        <v>9004.025125628141</v>
+        <v>10041.74390243902</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7691763066041959</v>
+        <v>0.7553238195623605</v>
       </c>
       <c r="K3" t="n">
-        <v>177.9095477386935</v>
+        <v>178.2743902439024</v>
       </c>
       <c r="L3" t="n">
-        <v>561.3869346733668</v>
+        <v>580.5365853658536</v>
       </c>
     </row>
     <row r="4">
@@ -577,31 +577,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1467</v>
+        <v>1658</v>
       </c>
       <c r="E4" t="n">
-        <v>1275064.45041441</v>
+        <v>1431923.899788656</v>
       </c>
       <c r="F4" t="n">
-        <v>3858.568507157464</v>
+        <v>3610.428829915561</v>
       </c>
       <c r="G4" t="n">
-        <v>4976.468984321745</v>
+        <v>5327.346200241254</v>
       </c>
       <c r="H4" t="n">
-        <v>28623.5269256987</v>
+        <v>27137.8974668275</v>
       </c>
       <c r="I4" t="n">
-        <v>3972.183367416496</v>
+        <v>3707.339565741858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2991492254986043</v>
+        <v>0.2880084127489949</v>
       </c>
       <c r="K4" t="n">
-        <v>233.5446489434219</v>
+        <v>223.9427020506635</v>
       </c>
       <c r="L4" t="n">
-        <v>617.8977505112474</v>
+        <v>597.4071170084439</v>
       </c>
     </row>
     <row r="5">
@@ -661,31 +661,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1117</v>
+        <v>913</v>
       </c>
       <c r="E6" t="n">
-        <v>852059.374444106</v>
+        <v>689366.814697971</v>
       </c>
       <c r="F6" t="n">
-        <v>1136.401969561325</v>
+        <v>1021.184008762322</v>
       </c>
       <c r="G6" t="n">
-        <v>685.9749328558639</v>
+        <v>662.3636363636364</v>
       </c>
       <c r="H6" t="n">
-        <v>6564.294538943599</v>
+        <v>6204.797371303395</v>
       </c>
       <c r="I6" t="n">
-        <v>767.0519247985676</v>
+        <v>820.4633077765608</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1378374385640029</v>
+        <v>0.1443114153738662</v>
       </c>
       <c r="K6" t="n">
-        <v>138.4341987466428</v>
+        <v>122.6210295728368</v>
       </c>
       <c r="L6" t="n">
-        <v>327.7108325872874</v>
+        <v>313.2968236582694</v>
       </c>
     </row>
     <row r="7">
@@ -703,31 +703,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="E7" t="n">
-        <v>321596.603558138</v>
+        <v>288573.484798051</v>
       </c>
       <c r="F7" t="n">
-        <v>979.3385416666666</v>
+        <v>930.3662790697674</v>
       </c>
       <c r="G7" t="n">
-        <v>35710.76302083334</v>
+        <v>36614.34011627907</v>
       </c>
       <c r="H7" t="n">
-        <v>43334.515625</v>
+        <v>44501.8023255814</v>
       </c>
       <c r="I7" t="n">
-        <v>2175.989583333333</v>
+        <v>2298.337209302325</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8479764098262436</v>
+        <v>0.8432373957593186</v>
       </c>
       <c r="K7" t="n">
-        <v>218.4427083333333</v>
+        <v>213.9360465116279</v>
       </c>
       <c r="L7" t="n">
-        <v>482.4375</v>
+        <v>490.2441860465116</v>
       </c>
     </row>
     <row r="8">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>953</v>
+        <v>1197</v>
       </c>
       <c r="E8" t="n">
-        <v>718031.96706191</v>
+        <v>913747.6455681321</v>
       </c>
       <c r="F8" t="n">
-        <v>2377.614900314795</v>
+        <v>2221.30910609858</v>
       </c>
       <c r="G8" t="n">
-        <v>6541.252885624344</v>
+        <v>6276.449456975773</v>
       </c>
       <c r="H8" t="n">
-        <v>22063.82896117524</v>
+        <v>20071.8462823726</v>
       </c>
       <c r="I8" t="n">
-        <v>1203.211962224554</v>
+        <v>1085.486215538847</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4593344298822832</v>
+        <v>0.4139541232661146</v>
       </c>
       <c r="K8" t="n">
-        <v>248.7985309548793</v>
+        <v>242.3316624895572</v>
       </c>
       <c r="L8" t="n">
-        <v>450.3389296956978</v>
+        <v>439.2631578947368</v>
       </c>
     </row>
     <row r="9">
@@ -829,31 +829,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>557</v>
+        <v>471</v>
       </c>
       <c r="E10" t="n">
-        <v>458879.1912557</v>
+        <v>386086.0075921</v>
       </c>
       <c r="F10" t="n">
-        <v>1221.912028725314</v>
+        <v>1114.087048832272</v>
       </c>
       <c r="G10" t="n">
-        <v>446.6068222621185</v>
+        <v>393.4819532908705</v>
       </c>
       <c r="H10" t="n">
-        <v>5614.662477558349</v>
+        <v>5344.031847133758</v>
       </c>
       <c r="I10" t="n">
-        <v>1446.222621184919</v>
+        <v>1506.736730360934</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06684200853407909</v>
+        <v>0.06669814750871503</v>
       </c>
       <c r="K10" t="n">
-        <v>118.3303411131059</v>
+        <v>111.6305732484076</v>
       </c>
       <c r="L10" t="n">
-        <v>375.8438061041293</v>
+        <v>365.3970276008492</v>
       </c>
     </row>
     <row r="11">
@@ -871,31 +871,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="E11" t="n">
-        <v>159157.573467</v>
+        <v>147825.5139852</v>
       </c>
       <c r="F11" t="n">
-        <v>1002.810344827586</v>
+        <v>954.6496815286624</v>
       </c>
       <c r="G11" t="n">
-        <v>37521.83908045977</v>
+        <v>37975.15923566879</v>
       </c>
       <c r="H11" t="n">
-        <v>47659.97126436781</v>
+        <v>48350.45222929936</v>
       </c>
       <c r="I11" t="n">
-        <v>8577.764367816091</v>
+        <v>8596.375796178343</v>
       </c>
       <c r="J11" t="n">
-        <v>0.791309664579941</v>
+        <v>0.797446096367326</v>
       </c>
       <c r="K11" t="n">
-        <v>206.8275862068965</v>
+        <v>200.7452229299363</v>
       </c>
       <c r="L11" t="n">
-        <v>573.3793103448276</v>
+        <v>575.4649681528663</v>
       </c>
     </row>
     <row r="12">
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1493</v>
+        <v>1596</v>
       </c>
       <c r="E12" t="n">
-        <v>1296835.57385664</v>
+        <v>1380960.81700204</v>
       </c>
       <c r="F12" t="n">
-        <v>4054.607501674481</v>
+        <v>3906.020050125313</v>
       </c>
       <c r="G12" t="n">
-        <v>5029.320830542531</v>
+        <v>5099.565162907268</v>
       </c>
       <c r="H12" t="n">
-        <v>30362.86537173476</v>
+        <v>29225.50125313283</v>
       </c>
       <c r="I12" t="n">
-        <v>4385.841259209645</v>
+        <v>4252.402255639097</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2812671762841372</v>
+        <v>0.2745845300603595</v>
       </c>
       <c r="K12" t="n">
-        <v>242.3436034829203</v>
+        <v>237.8583959899749</v>
       </c>
       <c r="L12" t="n">
-        <v>688.8774279973209</v>
+        <v>673.6572681704261</v>
       </c>
     </row>
     <row r="13">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1078</v>
+        <v>947</v>
       </c>
       <c r="E14" t="n">
-        <v>800322.4850499</v>
+        <v>698724.8927522</v>
       </c>
       <c r="F14" t="n">
-        <v>1150.917439703154</v>
+        <v>1071.454065469905</v>
       </c>
       <c r="G14" t="n">
-        <v>628.8200371057513</v>
+        <v>614.1055966209082</v>
       </c>
       <c r="H14" t="n">
-        <v>6185.497217068646</v>
+        <v>5902.702217529039</v>
       </c>
       <c r="I14" t="n">
-        <v>513.252319109462</v>
+        <v>550.4139387539599</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1355212161204174</v>
+        <v>0.1361946973122234</v>
       </c>
       <c r="K14" t="n">
-        <v>150.7031539888683</v>
+        <v>143.9915522703274</v>
       </c>
       <c r="L14" t="n">
-        <v>344.9378478664193</v>
+        <v>336.4720168954593</v>
       </c>
     </row>
     <row r="15">
@@ -1039,31 +1039,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="E15" t="n">
-        <v>291541.2845907</v>
+        <v>268020.3509445</v>
       </c>
       <c r="F15" t="n">
-        <v>1062.508333333333</v>
+        <v>1027.625</v>
       </c>
       <c r="G15" t="n">
-        <v>33917.08333333334</v>
+        <v>34421.18902439025</v>
       </c>
       <c r="H15" t="n">
-        <v>40202.07777777778</v>
+        <v>41216.01829268293</v>
       </c>
       <c r="I15" t="n">
-        <v>2871.472222222222</v>
+        <v>2925.798780487805</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8649897332519619</v>
+        <v>0.8609662638320779</v>
       </c>
       <c r="K15" t="n">
-        <v>256.6166666666667</v>
+        <v>253.4451219512195</v>
       </c>
       <c r="L15" t="n">
-        <v>480.8694444444445</v>
+        <v>493.2682926829268</v>
       </c>
     </row>
     <row r="16">
@@ -1081,31 +1081,31 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1076</v>
+        <v>1239</v>
       </c>
       <c r="E16" t="n">
-        <v>802752.99118207</v>
+        <v>927871.51712597</v>
       </c>
       <c r="F16" t="n">
-        <v>2492.848513011153</v>
+        <v>2383.994350282486</v>
       </c>
       <c r="G16" t="n">
-        <v>6642.842007434944</v>
+        <v>6589.191283292978</v>
       </c>
       <c r="H16" t="n">
-        <v>20573.34107806691</v>
+        <v>19506.79257465698</v>
       </c>
       <c r="I16" t="n">
-        <v>1341.520446096654</v>
+        <v>1250.676351896691</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4432555214267294</v>
+        <v>0.4221612615916706</v>
       </c>
       <c r="K16" t="n">
-        <v>282.1291821561338</v>
+        <v>273.5439870863599</v>
       </c>
       <c r="L16" t="n">
-        <v>491.2946096654275</v>
+        <v>478.7393058918483</v>
       </c>
     </row>
     <row r="17">
